--- a/assets/docs/lop3/Hoat dong trai nghiem - Lop 3.xlsx
+++ b/assets/docs/lop3/Hoat dong trai nghiem - Lop 3.xlsx
@@ -1416,7 +1416,8 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 4.2 CB1a: HS cùng lớp thống nhất nội quy ứng xử với bạn cả khi gặp mặt và khi nhắn tin.</t>
+          <t>Năng lực số 4.2 CB1a: HS cùng lớp thống nhất nội quy ứng xử với bạn cả khi gặp mặt và khi nhắn tin.
+Học tập và làm theo Bác: Điều 3 “Đoàn kết tốt, kỉ luật tốt” (mạch 3): nhóm phân công trang trí lớp “xanh – sạch – đẹp”; mỗi HS nhận và làm đúng phần việc của mình, cùng bạn hoàn thành ý tưởng chung ở tiết sinh hoạt lớp.</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2389,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Trước Tết</t>
+          <t>Chủ đề: Gia đình yêu thương</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr"/>
@@ -2422,7 +2423,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Trước Tết</t>
+          <t>Chủ đề: Gia đình yêu thương</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr"/>
@@ -2457,7 +2458,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Trước Tết</t>
+          <t>Chủ đề: Gia đình yêu thương</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr"/>
@@ -2492,7 +2493,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Trước Tết</t>
+          <t>Chủ đề: Gia đình yêu thương</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr"/>
@@ -2526,7 +2527,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Trước Tết</t>
+          <t>Chủ đề: Gia đình yêu thương</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr"/>
@@ -2561,7 +2562,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Trước Tết</t>
+          <t>Chủ đề: Gia đình yêu thương</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr"/>
@@ -3000,7 +3001,7 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Ăn uống an toàn, hợp vệ sinh</t>
+          <t>Chủ đề: Hoạt động vì cộng đồng</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr"/>
@@ -3036,7 +3037,7 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Ăn uống an toàn, hợp vệ sinh</t>
+          <t>Chủ đề: Hoạt động vì cộng đồng</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr"/>
@@ -3071,7 +3072,7 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Ăn uống an toàn, hợp vệ sinh</t>
+          <t>Chủ đề: Hoạt động vì cộng đồng</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr"/>
@@ -3107,7 +3108,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Ăn uống an toàn, hợp vệ sinh</t>
+          <t>Chủ đề: Hoạt động vì cộng đồng</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr"/>
@@ -3131,7 +3132,8 @@
         <is>
           <t>GDĐP: - Mô tả được một số hoạt động tết vì người nghèo ở quê hương em; - Hiểu được một cách đơn giản ý nghĩa tết vì người nghèo ở quê hương em; - Tham gia được một số hoạt động để giúp đỡ hộ nghèo vào ngày Tết ở quê em phù hợp với bản thân.
 Năng lực số 2.2 CB1a: HS nhận biết kênh số phù hợp của lớp để chia sẻ, tuyên truyền nội dung theo chủ điểm.
-STEM: Hoạt động trải nghiệm STEM học kì II: ngày hội/câu lạc bộ/dự án STEM cấp lớp hoặc khối — tối thiểu 01 lần mỗi học kì (CV 3132/SGD&amp;ĐT); HS trưng bày, giới thiệu sản phẩm từ các bài học STEM.</t>
+STEM: Hoạt động trải nghiệm STEM học kì II: ngày hội/câu lạc bộ/dự án STEM cấp lớp hoặc khối — tối thiểu 01 lần mỗi học kì (CV 3132/SGD&amp;ĐT); HS trưng bày, giới thiệu sản phẩm từ các bài học STEM.
+QPAN: Tổ chức tham quan di tích lịch sử, nhà truyền thống ở địa phương hoặc xem tư liệu thay thế; giáo dục tự hào về truyền thống dân tộc; rèn tính kỉ luật, tinh thần đoàn kết.</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3145,7 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Ăn uống an toàn, hợp vệ sinh</t>
+          <t>Chủ đề: Hoạt động vì cộng đồng</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr"/>
@@ -3178,7 +3180,7 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Ăn uống an toàn, hợp vệ sinh</t>
+          <t>Chủ đề: Hoạt động vì cộng đồng</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr"/>
@@ -3208,7 +3210,7 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Ăn uống an toàn, hợp vệ sinh</t>
+          <t>Chủ đề: Hoạt động vì cộng đồng</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr"/>
@@ -3242,7 +3244,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Ăn uống an toàn, hợp vệ sinh</t>
+          <t>Chủ đề: Hoạt động vì cộng đồng</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr"/>
@@ -3278,7 +3280,7 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Ăn uống an toàn, hợp vệ sinh</t>
+          <t>Chủ đề: Hoạt động vì cộng đồng</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr"/>
